--- a/Codigos/Windows/TF_HBI_Gaussiana.xlsx
+++ b/Codigos/Windows/TF_HBI_Gaussiana.xlsx
@@ -413,303 +413,311 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B1" t="n">
-        <v>0.005525501961667179</v>
+        <v>5.485076713673931e-06</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01413102032272865</v>
+        <v>2.339326022090295e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02700615403981892</v>
+        <v>7.762225470477827e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04551144318256293</v>
+        <v>0.0002299302680475719</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0710625323088221</v>
+        <v>0.0006266877640254883</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1049541557856225</v>
+        <v>0.001585290609359415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>0.14814033110054</v>
+        <v>0.003733435013886296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>0.201005123183608</v>
+        <v>0.008198208362670325</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2631718108268286</v>
+        <v>0.01680510420738959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n">
-        <v>0.333401111194264</v>
+        <v>0.03219390803835313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4096175004746547</v>
+        <v>0.05771353756354874</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4890773637322227</v>
+        <v>0.09696492864738575</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5686596974987213</v>
+        <v>0.152959629169655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6452290443770288</v>
+        <v>0.2270479898282266</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7160012334424195</v>
+        <v>0.3179689953688732</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7788417476212148</v>
+        <v>0.4214569159838827</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8324443956997553</v>
+        <v>0.5307081313759757</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8763684252516396</v>
+        <v>0.6376811076432404</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9109454419258426</v>
+        <v>0.7348289293340308</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9370936708287857</v>
+        <v>0.8166571750528078</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9560898584957254</v>
+        <v>0.8805842156584192</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9693473097559591</v>
+        <v>0.9269051323045252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9782356985133021</v>
+        <v>0.9580352581197537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9839604344392325</v>
+        <v>0.9774394603655038</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9875025056593201</v>
+        <v>0.9886576272109815</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9896078761667007</v>
+        <v>0.9946729534069086</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9908100553265479</v>
+        <v>0.9976645818721678</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n">
-        <v>0.9914695013742096</v>
+        <v>0.9990445444729812</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9918170045347052</v>
+        <v>0.9996349333433576</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9919929214748383</v>
+        <v>0.9998692052396825</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9920784726501777</v>
+        <v>0.9999554263100252</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9921184407694756</v>
+        <v>0.9999848581770383</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9921363786389701</v>
+        <v>0.9999941764065022</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9921441125188332</v>
+        <v>0.999996912684227</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n">
-        <v>0.992147315787735</v>
+        <v>0.9999976579276207</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9921485903433424</v>
+        <v>0.9999978461829505</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n">
-        <v>0.9921490775279885</v>
+        <v>0.9999978902899599</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.9999978998746732</v>
       </c>
     </row>
   </sheetData>
